--- a/data/dividends_info_20260302.xlsx
+++ b/data/dividends_info_20260302.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>54.84999847412109</v>
+        <v>53.34999847412109</v>
       </c>
       <c r="I2" t="n">
-        <v>1.276207875065427</v>
+        <v>1.312090009411255</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -538,11 +538,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -551,12 +551,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -566,30 +566,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IT0003796171</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>22.75</v>
+        <v>6.994999885559082</v>
       </c>
       <c r="I3" t="n">
-        <v>3.736263736263736</v>
+        <v>7.147962947536731</v>
       </c>
       <c r="J3" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="K3" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.04</v>
+        <v>0.54</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -598,12 +598,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -613,30 +613,30 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IT0004764699</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>82.33999633789062</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="I4" t="n">
-        <v>1.263055679201458</v>
+        <v>4.433497425862394</v>
       </c>
       <c r="J4" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2</v>
+        <v>3.615</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -645,45 +645,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IT0001031084</t>
+          <t>NL0011585146</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>54.84999847412109</v>
+        <v>308.2999877929688</v>
       </c>
       <c r="I5" t="n">
-        <v>4.010939035919914</v>
+        <v>1.172559242015788</v>
       </c>
       <c r="J5" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.79</v>
+        <v>1.36</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -692,12 +692,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,30 +707,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0005144784</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19.98999977111816</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="I6" t="n">
-        <v>3.951976033243398</v>
+        <v>5.190839543500142</v>
       </c>
       <c r="J6" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -739,12 +739,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -754,30 +754,30 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0000062957</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.835000038146973</v>
+        <v>18.07999992370605</v>
       </c>
       <c r="I7" t="n">
-        <v>3.256212489423368</v>
+        <v>3.484513289040224</v>
       </c>
       <c r="J7" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="K7" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.4</v>
+        <v>0.26</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,45 +786,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>58.43999862670898</v>
+        <v>20.3700008392334</v>
       </c>
       <c r="I8" t="n">
-        <v>2.395619495035639</v>
+        <v>1.276386790810681</v>
       </c>
       <c r="J8" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -833,45 +833,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>NL0000226223</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.1200008392334</v>
+        <v>28.17000007629395</v>
       </c>
       <c r="I9" t="n">
-        <v>2.595155615140949</v>
+        <v>0.3194888170260894</v>
       </c>
       <c r="J9" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Giocamondo Study S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5105</v>
+        <v>0.06</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -880,12 +880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -895,30 +895,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005652489</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9.119999885559082</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="I10" t="n">
-        <v>5.597587789538714</v>
+        <v>3.749999944120646</v>
       </c>
       <c r="J10" t="n">
-        <v>63</v>
+        <v>-21</v>
       </c>
       <c r="K10" t="n">
-        <v>65</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.75</v>
+        <v>0.06</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -927,12 +927,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -942,677 +942,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0004674666</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19.39999961853027</v>
+        <v>0.1770000010728836</v>
       </c>
       <c r="I11" t="n">
-        <v>3.865979457461552</v>
+        <v>33.89830487927155</v>
       </c>
       <c r="J11" t="n">
-        <v>63</v>
+        <v>-28</v>
       </c>
       <c r="K11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>IT0005322612</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>4.364999771118164</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.43642629702991</v>
-      </c>
-      <c r="J12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K12" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EDISON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IT0003372205</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>2.234999895095825</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.908277541427497</v>
-      </c>
-      <c r="J13" t="n">
-        <v>56</v>
-      </c>
-      <c r="K13" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>IT0004998065</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>6.880000114440918</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.267441739579549</v>
-      </c>
-      <c r="J14" t="n">
-        <v>49</v>
-      </c>
-      <c r="K14" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>IT0005218380</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>12.53499984741211</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.30793782667245</v>
-      </c>
-      <c r="J15" t="n">
-        <v>49</v>
-      </c>
-      <c r="K15" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.615</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NL0011585146</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>321.3999938964844</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.124766667283855</v>
-      </c>
-      <c r="J16" t="n">
-        <v>49</v>
-      </c>
-      <c r="K16" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>IT0005144784</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>26.39999961853027</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5.151515225952543</v>
-      </c>
-      <c r="J17" t="n">
-        <v>49</v>
-      </c>
-      <c r="K17" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>IT0000062957</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>18.46999931335449</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.410936780839438</v>
-      </c>
-      <c r="J18" t="n">
-        <v>49</v>
-      </c>
-      <c r="K18" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>IT0004176001</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.878048780487805</v>
-      </c>
-      <c r="J19" t="n">
-        <v>49</v>
-      </c>
-      <c r="K19" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.7208</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>IT0005239360</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>72.41000366210938</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.3764672185764</v>
-      </c>
-      <c r="J20" t="n">
-        <v>49</v>
-      </c>
-      <c r="K20" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>IT0003132476</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>19.6560001373291</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.322751313509755</v>
-      </c>
-      <c r="J21" t="n">
-        <v>21</v>
-      </c>
-      <c r="K21" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>28.40999984741211</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.3167898644258464</v>
-      </c>
-      <c r="J22" t="n">
-        <v>21</v>
-      </c>
-      <c r="K22" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>IT0001031084</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>54.84999847412109</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.185050169703611</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Giocamondo Study S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>IT0005652489</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1.700000047683716</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.529411665708551</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>H-FARM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Straordinario</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>IT0004674666</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1829999983310699</v>
-      </c>
-      <c r="I25" t="n">
-        <v>32.78688554491267</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K25" t="n">
         <v>-26</v>
       </c>
     </row>
@@ -1627,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C394"/>
+  <dimension ref="A1:C404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1837,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1847,7 +1189,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1281,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,14 +1291,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1973,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1990,7 +1332,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2000,7 +1342,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2085,14 +1427,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2102,14 +1444,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2119,14 +1461,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2153,14 +1495,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2170,7 +1512,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -2330,7 +1672,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2347,7 +1689,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2364,7 +1706,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2374,14 +1716,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2391,14 +1733,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2415,7 +1757,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2432,7 +1774,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Banca Popolare di Sondrio S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2449,7 +1791,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2466,7 +1808,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Banca Popolare di Sondrio S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2483,7 +1825,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2500,7 +1842,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2517,7 +1859,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2527,14 +1869,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2544,14 +1886,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2568,7 +1910,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2578,14 +1920,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2636,7 +1978,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2663,7 +2005,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2029,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2721,7 +2063,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2738,7 +2080,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2755,7 +2097,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2772,7 +2114,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2789,7 +2131,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2799,14 +2141,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2823,7 +2165,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2833,14 +2175,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2857,7 +2199,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2874,7 +2216,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2891,7 +2233,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2908,7 +2250,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2925,7 +2267,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2942,7 +2284,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2959,7 +2301,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2976,7 +2318,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2993,7 +2335,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3010,7 +2352,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3027,7 +2369,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3037,14 +2379,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3061,7 +2403,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3078,7 +2420,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3088,14 +2430,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3112,7 +2454,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3129,7 +2471,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3139,14 +2481,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3163,7 +2505,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3173,14 +2515,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3197,7 +2539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3214,7 +2556,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3224,14 +2566,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3241,14 +2583,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3258,14 +2600,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3282,7 +2624,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3299,7 +2641,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3309,14 +2651,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3333,7 +2675,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3350,12 +2692,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3367,29 +2709,29 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3401,12 +2743,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3418,41 +2760,41 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3462,7 +2804,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3479,14 +2821,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3503,7 +2845,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3520,12 +2862,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3537,29 +2879,29 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3571,12 +2913,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3588,29 +2930,29 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3622,46 +2964,46 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3015,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3707,7 +3049,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3724,7 +3066,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3741,7 +3083,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3751,14 +3093,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3768,14 +3110,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3792,7 +3134,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3809,7 +3151,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3826,7 +3168,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3836,70 +3178,70 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3911,12 +3253,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3928,12 +3270,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3945,12 +3287,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3962,46 +3304,46 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4013,12 +3355,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4030,46 +3372,46 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4081,29 +3423,29 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4115,12 +3457,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4132,12 +3474,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4149,29 +3491,29 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4183,29 +3525,29 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4217,12 +3559,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4234,29 +3576,29 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4268,12 +3610,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4285,12 +3627,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4302,29 +3644,29 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4336,24 +3678,24 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4370,7 +3712,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4387,7 +3729,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4404,7 +3746,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4414,14 +3756,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4431,7 +3773,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4455,7 +3797,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4472,12 +3814,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4489,12 +3831,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4506,29 +3848,29 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4540,29 +3882,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4574,12 +3916,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4591,12 +3933,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4608,12 +3950,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4625,12 +3967,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4642,12 +3984,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4659,12 +4001,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4676,12 +4018,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4693,12 +4035,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4710,12 +4052,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4727,12 +4069,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4744,12 +4086,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4761,29 +4103,29 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4795,7 +4137,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4812,7 +4154,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4829,7 +4171,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4846,7 +4188,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4856,14 +4198,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4880,7 +4222,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4897,7 +4239,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4914,7 +4256,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4924,14 +4266,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4941,14 +4283,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4965,7 +4307,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4982,7 +4324,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4992,14 +4334,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5016,7 +4358,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5033,12 +4375,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5050,29 +4392,29 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5084,12 +4426,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5101,12 +4443,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5118,12 +4460,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5135,29 +4477,29 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5169,12 +4511,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5186,12 +4528,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5203,7 +4545,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5213,14 +4555,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5237,7 +4579,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5247,14 +4589,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5271,7 +4613,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5288,7 +4630,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5305,7 +4647,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5315,19 +4657,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5339,29 +4681,29 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5373,46 +4715,46 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5424,12 +4766,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5441,12 +4783,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5458,12 +4800,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5475,12 +4817,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5492,7 +4834,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5509,7 +4851,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5519,14 +4861,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5536,14 +4878,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5560,7 +4902,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5577,7 +4919,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5594,7 +4936,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5604,14 +4946,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5621,14 +4963,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5645,7 +4987,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5662,7 +5004,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5679,7 +5021,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5696,12 +5038,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5713,12 +5055,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5730,12 +5072,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5747,63 +5089,63 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5815,12 +5157,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5832,12 +5174,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5849,24 +5191,24 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5883,7 +5225,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5900,7 +5242,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5917,7 +5259,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5927,14 +5269,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5944,14 +5286,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5968,7 +5310,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5978,14 +5320,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5995,14 +5337,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6019,7 +5361,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6036,7 +5378,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6053,7 +5395,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6070,7 +5412,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6080,14 +5422,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6097,14 +5439,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6114,14 +5456,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6138,7 +5480,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6172,7 +5514,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6189,12 +5531,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6206,29 +5548,29 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6240,12 +5582,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6257,29 +5599,29 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6291,12 +5633,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6308,12 +5650,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6325,12 +5667,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6342,12 +5684,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6359,7 +5701,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6376,7 +5718,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6393,7 +5735,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6410,7 +5752,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6427,7 +5769,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6444,7 +5786,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6461,7 +5803,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6478,7 +5820,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6488,14 +5830,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6512,7 +5854,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6529,7 +5871,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6546,7 +5888,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6563,7 +5905,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6580,7 +5922,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6597,7 +5939,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6614,7 +5956,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6624,14 +5966,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6648,7 +5990,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6665,7 +6007,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6682,7 +6024,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6699,7 +6041,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6716,7 +6058,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6733,7 +6075,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6750,7 +6092,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6760,14 +6102,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6777,14 +6119,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6801,12 +6143,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -6818,12 +6160,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -6835,12 +6177,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -6852,12 +6194,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -6869,12 +6211,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -6886,12 +6228,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -6903,12 +6245,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -6920,12 +6262,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -6937,12 +6279,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6954,12 +6296,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -6971,7 +6313,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -6988,7 +6330,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7005,7 +6347,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7022,7 +6364,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7032,14 +6374,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7056,7 +6398,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7073,7 +6415,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7090,7 +6432,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7107,7 +6449,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7124,7 +6466,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7141,7 +6483,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7158,7 +6500,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7175,7 +6517,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7185,14 +6527,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7209,7 +6551,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7226,7 +6568,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7236,14 +6578,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7260,7 +6602,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7277,7 +6619,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -7287,14 +6629,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7311,7 +6653,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7328,7 +6670,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7345,7 +6687,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7362,7 +6704,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7372,14 +6714,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7396,7 +6738,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7413,7 +6755,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7423,14 +6765,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7440,14 +6782,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -7464,7 +6806,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7481,7 +6823,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7491,14 +6833,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7515,7 +6857,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7532,7 +6874,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -7549,7 +6891,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7566,7 +6908,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -7583,7 +6925,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -7600,7 +6942,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -7617,7 +6959,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -7634,7 +6976,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -7651,7 +6993,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -7668,7 +7010,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -7685,7 +7027,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -7702,12 +7044,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -7719,12 +7061,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -7736,12 +7078,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -7753,29 +7095,29 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -7787,12 +7129,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -7804,46 +7146,46 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -7855,24 +7197,24 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -7889,7 +7231,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -7906,7 +7248,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -7923,7 +7265,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -7933,14 +7275,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -7957,7 +7299,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -7974,7 +7316,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -7984,14 +7326,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -8001,14 +7343,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -8025,7 +7367,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -8042,7 +7384,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -8052,14 +7394,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -8069,14 +7411,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -8093,7 +7435,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -8110,7 +7452,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -8127,7 +7469,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -8137,14 +7479,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -8161,7 +7503,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -8178,7 +7520,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -8195,7 +7537,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -8212,7 +7554,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -8229,7 +7571,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -8246,7 +7588,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -8263,7 +7605,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -8280,7 +7622,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -8297,7 +7639,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -8314,15 +7656,185 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
+          <t>MONDO TV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DigiTouch S.p.A.</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Dedem S.p.A.</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Com.Tel S.p.A.</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>CleanBnB S.p.A.</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>NEUROSOFT</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>OPS ECOM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>OPS Retail S.p.A.</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
           <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>DigiTouch S.p.A.</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>GEL S.p.A.</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
         <is>
           <t>Bod Annual Report</t>
         </is>
@@ -8352,61 +7864,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Technoprobe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>